--- a/ai-review/ai-track-stocks-20260918.xlsx
+++ b/ai-review/ai-track-stocks-20260918.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>AI 芯片的制造与上游：晶圆制造（半导体）· 设备 · 材料。国产替代 + 景气周期双重属性，本轮由晶圆双雄 Q2 超预期点燃。</t>
+          <t>AI 芯片的制造与上游：晶圆制造（半导体）· 设备 · 材料。国产替代 + 景气周期双重属性。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AIPC / AI 手机</t>
+          <t>AIPC / AI手机</t>
         </is>
       </c>
     </row>
